--- a/light_fight/Assets/Excels/PlayerConfig.xlsx
+++ b/light_fight/Assets/Excels/PlayerConfig.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">level</t>
+    <t xml:space="preserve">Level</t>
   </si>
   <si>
-    <t xml:space="preserve">expRequire</t>
+    <t xml:space="preserve">Exp</t>
   </si>
 </sst>
 </file>
@@ -35,7 +35,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,6 +57,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -109,20 +116,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -387,830 +402,830 @@
   <dimension ref="A1:H102"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="12.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="5" t="n">
         <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>405</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>535</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="5" t="n">
         <v>665</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>730</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="5" t="n">
         <v>795</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="5" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="5" t="n">
         <v>925</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="5" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="5" t="n">
         <v>1055</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="5" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="5" t="n">
         <v>1185</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="5" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="5" t="n">
         <v>1315</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="5" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="5" t="n">
         <v>1445</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="5" t="n">
         <v>1510</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="5" t="n">
         <v>1575</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="5" t="n">
         <v>1640</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="5" t="n">
         <v>1705</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="5" t="n">
         <v>1770</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="5" t="n">
         <v>1835</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="5" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="5" t="n">
         <v>1965</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="5" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="5" t="n">
         <v>2095</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="5" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="5" t="n">
         <v>2225</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="5" t="n">
         <v>2290</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="5" t="n">
         <v>2355</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="5" t="n">
         <v>2420</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="5" t="n">
         <v>2485</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="5" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="5" t="n">
         <v>2615</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="5" t="n">
         <v>2680</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="5" t="n">
         <v>2745</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="5" t="n">
         <v>2810</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" s="5" t="n">
         <v>2875</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="5" t="n">
         <v>2940</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="5" t="n">
         <v>3005</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="5" t="n">
         <v>3070</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="5" t="n">
         <v>3135</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="5" t="n">
         <v>3200</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="5" t="n">
         <v>3265</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="5" t="n">
         <v>3330</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="5" t="n">
         <v>3395</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="5" t="n">
         <v>3460</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="5" t="n">
         <v>3525</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="5" t="n">
         <v>3590</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="5" t="n">
         <v>3655</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="5" t="n">
         <v>3720</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="5" t="n">
         <v>3785</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" s="5" t="n">
         <v>3850</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="5" t="n">
         <v>3915</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="5" t="n">
         <v>3980</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="5" t="n">
         <v>4045</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="5" t="n">
         <v>4110</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="5" t="n">
         <v>4175</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" s="5" t="n">
         <v>4240</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="5" t="n">
         <v>4305</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="5" t="n">
         <v>4370</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="5" t="n">
         <v>4435</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="5" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="5" t="n">
         <v>4565</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="5" t="n">
         <v>4630</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="5" t="n">
         <v>4695</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="5" t="n">
         <v>4760</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="5" t="n">
         <v>4825</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="5" t="n">
         <v>4890</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="5" t="n">
         <v>4955</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="5" t="n">
         <v>5020</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="5" t="n">
         <v>5085</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="5" t="n">
         <v>5150</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="5" t="n">
         <v>5215</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="5" t="n">
         <v>5280</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="5" t="n">
         <v>5345</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="5" t="n">
         <v>5410</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" s="5" t="n">
         <v>5475</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="5" t="n">
         <v>5540</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" s="5" t="n">
         <v>5605</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" s="5" t="n">
         <v>5670</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" s="5" t="n">
         <v>5735</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" s="5" t="n">
         <v>5800</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" s="5" t="n">
         <v>5865</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="5" t="n">
         <v>5930</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" s="5" t="n">
         <v>5995</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" s="5" t="n">
         <v>6060</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" s="5" t="n">
         <v>6125</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" s="5" t="n">
         <v>6190</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" s="5" t="n">
         <v>6255</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" s="5" t="n">
         <v>6320</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" s="5" t="n">
         <v>6385</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" s="5" t="n">
         <v>6450</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" s="5" t="n">
         <v>6515</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/PlayerConfig.xlsx
+++ b/light_fight/Assets/Excels/PlayerConfig.xlsx
@@ -399,7 +399,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.97"/>
@@ -423,816 +423,809 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>275</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>340</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>405</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>470</v>
+        <v>535</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>535</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>600</v>
+        <v>665</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>665</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>730</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>795</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>860</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>925</v>
+        <v>990</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>990</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1055</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1120</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>1185</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1250</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1315</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1380</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1445</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1510</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1575</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1640</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1705</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1770</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1835</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1965</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2030</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2095</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>2160</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>2225</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>2290</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2355</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>2420</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>2485</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>2550</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>2615</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>2680</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>2745</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2810</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2875</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>2940</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>3005</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>3070</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>3135</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>3200</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>3265</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>3330</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>3395</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>3460</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>3525</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3590</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>3655</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>3720</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>3785</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>3850</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>3915</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>3980</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>4045</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>4110</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>4175</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>4240</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>4305</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>4370</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>4435</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>4500</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>4565</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>4630</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>4695</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>4760</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>4825</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>4890</v>
+        <v>4955</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>4955</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>5020</v>
+        <v>5085</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>5085</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>5150</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>5215</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>5280</v>
+        <v>5345</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>5345</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>5410</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>5475</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>5540</v>
+        <v>5605</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>5605</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>5670</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>5735</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>5800</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>5865</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>5930</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>5995</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>6060</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>6125</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>6190</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>6255</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>6320</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>6385</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>6450</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" s="5" t="n">
         <v>6515</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="C1:H431">
+  <conditionalFormatting sqref="C1:H430">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>MOD($A1048575,2)=1</formula>
+      <formula>MOD($A1048574,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
